--- a/erp-server/erp-server-wms/src/main/resources/excel/b2cDeliveryOrderExport.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/b2cDeliveryOrderExport.xlsx
@@ -1151,7 +1151,7 @@
     <col min="4" max="4" width="12.5" style="2" customWidth="1"/>
     <col min="5" max="5" width="9.75" style="2" customWidth="1"/>
     <col min="6" max="6" width="11.75" style="2" customWidth="1"/>
-    <col min="7" max="7" width="11.375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="26.25" style="2" customWidth="1"/>
     <col min="8" max="8" width="14.25" style="2" customWidth="1"/>
     <col min="9" max="9" width="10.25" style="2" customWidth="1"/>
     <col min="10" max="10" width="11.875" style="2" customWidth="1"/>
@@ -1159,11 +1159,11 @@
     <col min="12" max="12" width="11.125" style="2" customWidth="1"/>
     <col min="13" max="13" width="10.625" style="2" customWidth="1"/>
     <col min="14" max="14" width="12" style="2" customWidth="1"/>
-    <col min="15" max="15" width="10.625" style="2" customWidth="1"/>
+    <col min="15" max="15" width="15.375" style="2" customWidth="1"/>
     <col min="16" max="16" width="10.75" style="2" customWidth="1"/>
-    <col min="17" max="17" width="14.875" style="2" customWidth="1"/>
-    <col min="18" max="18" width="12.875" style="2" customWidth="1"/>
-    <col min="19" max="19" width="14" style="2" customWidth="1"/>
+    <col min="17" max="17" width="18.25" style="2" customWidth="1"/>
+    <col min="18" max="18" width="17.375" style="2" customWidth="1"/>
+    <col min="19" max="19" width="17.625" style="2" customWidth="1"/>
     <col min="20" max="21" width="21.125" style="2" customWidth="1"/>
     <col min="22" max="22" width="21" style="2" customWidth="1"/>
     <col min="23" max="25" width="20.625" style="2" customWidth="1"/>

--- a/erp-server/erp-server-wms/src/main/resources/excel/b2cDeliveryOrderExport.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/b2cDeliveryOrderExport.xlsx
@@ -116,7 +116,7 @@
     <t>{.weighName}</t>
   </si>
   <si>
-    <t>{.weight}</t>
+    <t>{.weightName}</t>
   </si>
   <si>
     <t>{.skuNo}</t>

--- a/erp-server/erp-server-wms/src/main/resources/excel/b2cDeliveryOrderExport.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/b2cDeliveryOrderExport.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="24045" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>发货单号</t>
   </si>
@@ -41,6 +41,9 @@
     <t>销售单号</t>
   </si>
   <si>
+    <t>平台订单号</t>
+  </si>
+  <si>
     <t>单据状态</t>
   </si>
   <si>
@@ -77,6 +80,9 @@
     <t>仓位</t>
   </si>
   <si>
+    <t>备注</t>
+  </si>
+  <si>
     <t>创建时间</t>
   </si>
   <si>
@@ -86,6 +92,12 @@
     <t>发货时间</t>
   </si>
   <si>
+    <t>验货时间</t>
+  </si>
+  <si>
+    <t>称重时间</t>
+  </si>
+  <si>
     <t>{.code}</t>
   </si>
   <si>
@@ -98,6 +110,9 @@
     <t>{.soCode}</t>
   </si>
   <si>
+    <t>{.platformCode}</t>
+  </si>
+  <si>
     <t>{.statusName}</t>
   </si>
   <si>
@@ -134,6 +149,9 @@
     <t>{.warehouseLocation}</t>
   </si>
   <si>
+    <t>{.orderRemark}</t>
+  </si>
+  <si>
     <t>{.createTime}</t>
   </si>
   <si>
@@ -141,6 +159,12 @@
   </si>
   <si>
     <t>{.deliveryTime}</t>
+  </si>
+  <si>
+    <t>{.inspectionTime}</t>
+  </si>
+  <si>
+    <t>{.weighingTime}</t>
   </si>
 </sst>
 </file>
@@ -1142,35 +1166,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S2"/>
+  <dimension ref="A1:W2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="15" style="2" customWidth="1"/>
     <col min="2" max="2" width="11.375" style="2" customWidth="1"/>
     <col min="3" max="3" width="11.5" style="2" customWidth="1"/>
     <col min="4" max="4" width="12.5" style="2" customWidth="1"/>
-    <col min="5" max="5" width="9.75" style="2" customWidth="1"/>
-    <col min="6" max="6" width="11.75" style="2" customWidth="1"/>
-    <col min="7" max="7" width="26.25" style="2" customWidth="1"/>
-    <col min="8" max="8" width="14.25" style="2" customWidth="1"/>
-    <col min="9" max="9" width="10.25" style="2" customWidth="1"/>
-    <col min="10" max="10" width="11.875" style="2" customWidth="1"/>
-    <col min="11" max="11" width="12.125" style="2" customWidth="1"/>
-    <col min="12" max="12" width="11.125" style="2" customWidth="1"/>
-    <col min="13" max="13" width="10.625" style="2" customWidth="1"/>
-    <col min="14" max="14" width="12" style="2" customWidth="1"/>
-    <col min="15" max="15" width="15.375" style="2" customWidth="1"/>
-    <col min="16" max="16" width="10.75" style="2" customWidth="1"/>
-    <col min="17" max="17" width="18.25" style="2" customWidth="1"/>
-    <col min="18" max="18" width="17.375" style="2" customWidth="1"/>
-    <col min="19" max="19" width="17.625" style="2" customWidth="1"/>
-    <col min="20" max="21" width="21.125" style="2" customWidth="1"/>
-    <col min="22" max="22" width="21" style="2" customWidth="1"/>
-    <col min="23" max="25" width="20.625" style="2" customWidth="1"/>
-    <col min="26" max="16384" width="9" style="2"/>
+    <col min="5" max="5" width="14.25" style="2" customWidth="1"/>
+    <col min="6" max="6" width="9.75" style="2" customWidth="1"/>
+    <col min="7" max="7" width="11.75" style="2" customWidth="1"/>
+    <col min="8" max="8" width="26.25" style="2" customWidth="1"/>
+    <col min="9" max="9" width="14.25" style="2" customWidth="1"/>
+    <col min="10" max="10" width="10.25" style="2" customWidth="1"/>
+    <col min="11" max="11" width="11.875" style="2" customWidth="1"/>
+    <col min="12" max="12" width="12.125" style="2" customWidth="1"/>
+    <col min="13" max="13" width="11.125" style="2" customWidth="1"/>
+    <col min="14" max="14" width="10.625" style="2" customWidth="1"/>
+    <col min="15" max="15" width="12" style="2" customWidth="1"/>
+    <col min="16" max="16" width="15.375" style="2" customWidth="1"/>
+    <col min="17" max="17" width="10.75" style="2" customWidth="1"/>
+    <col min="18" max="18" width="21.875" style="2" customWidth="1"/>
+    <col min="19" max="19" width="18.25" style="2" customWidth="1"/>
+    <col min="20" max="20" width="17.375" style="2" customWidth="1"/>
+    <col min="21" max="23" width="17.625" style="2" customWidth="1"/>
+    <col min="24" max="26" width="20.625" style="2" customWidth="1"/>
+    <col min="27" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:19">
+    <row r="1" s="1" customFormat="1" spans="1:23">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1228,64 +1252,88 @@
       <c r="S1" s="3" t="s">
         <v>18</v>
       </c>
+      <c r="T1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="3" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="2" spans="1:19">
+    <row r="2" spans="1:23">
       <c r="A2" s="4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="S2" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
+      </c>
+      <c r="T2" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="U2" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="V2" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="W2" s="4" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-wms/src/main/resources/excel/b2cDeliveryOrderExport.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/b2cDeliveryOrderExport.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24045" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t>发货单号</t>
   </si>
@@ -56,6 +56,9 @@
     <t>拣货单状态</t>
   </si>
   <si>
+    <t>物流单状态</t>
+  </si>
+  <si>
     <t>验货状态</t>
   </si>
   <si>
@@ -123,6 +126,9 @@
   </si>
   <si>
     <t>{.printPickingName}</t>
+  </si>
+  <si>
+    <t>{.printLogisticName}</t>
   </si>
   <si>
     <t>{.inspectionName}</t>
@@ -1166,7 +1172,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W2"/>
+  <dimension ref="A1:X2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="15" style="2" customWidth="1"/>
@@ -1177,24 +1183,24 @@
     <col min="6" max="6" width="9.75" style="2" customWidth="1"/>
     <col min="7" max="7" width="11.75" style="2" customWidth="1"/>
     <col min="8" max="8" width="26.25" style="2" customWidth="1"/>
-    <col min="9" max="9" width="14.25" style="2" customWidth="1"/>
-    <col min="10" max="10" width="10.25" style="2" customWidth="1"/>
-    <col min="11" max="11" width="11.875" style="2" customWidth="1"/>
-    <col min="12" max="12" width="12.125" style="2" customWidth="1"/>
-    <col min="13" max="13" width="11.125" style="2" customWidth="1"/>
-    <col min="14" max="14" width="10.625" style="2" customWidth="1"/>
-    <col min="15" max="15" width="12" style="2" customWidth="1"/>
-    <col min="16" max="16" width="15.375" style="2" customWidth="1"/>
-    <col min="17" max="17" width="10.75" style="2" customWidth="1"/>
-    <col min="18" max="18" width="21.875" style="2" customWidth="1"/>
-    <col min="19" max="19" width="18.25" style="2" customWidth="1"/>
-    <col min="20" max="20" width="17.375" style="2" customWidth="1"/>
-    <col min="21" max="23" width="17.625" style="2" customWidth="1"/>
-    <col min="24" max="26" width="20.625" style="2" customWidth="1"/>
-    <col min="27" max="16384" width="9" style="2"/>
+    <col min="9" max="10" width="22.75" style="2" customWidth="1"/>
+    <col min="11" max="11" width="10.25" style="2" customWidth="1"/>
+    <col min="12" max="12" width="11.875" style="2" customWidth="1"/>
+    <col min="13" max="13" width="12.125" style="2" customWidth="1"/>
+    <col min="14" max="14" width="11.125" style="2" customWidth="1"/>
+    <col min="15" max="15" width="10.625" style="2" customWidth="1"/>
+    <col min="16" max="16" width="12" style="2" customWidth="1"/>
+    <col min="17" max="17" width="15.375" style="2" customWidth="1"/>
+    <col min="18" max="18" width="10.75" style="2" customWidth="1"/>
+    <col min="19" max="19" width="21.875" style="2" customWidth="1"/>
+    <col min="20" max="20" width="18.25" style="2" customWidth="1"/>
+    <col min="21" max="21" width="17.375" style="2" customWidth="1"/>
+    <col min="22" max="24" width="17.625" style="2" customWidth="1"/>
+    <col min="25" max="27" width="20.625" style="2" customWidth="1"/>
+    <col min="28" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:23">
+    <row r="1" s="1" customFormat="1" spans="1:24">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1264,76 +1270,82 @@
       <c r="W1" s="3" t="s">
         <v>22</v>
       </c>
+      <c r="X1" s="3" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="2" spans="1:23">
+    <row r="2" spans="1:24">
       <c r="A2" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="S2" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="U2" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="V2" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="W2" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="X2" s="4" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-wms/src/main/resources/excel/b2cDeliveryOrderExport.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/b2cDeliveryOrderExport.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
   <si>
     <t>发货单号</t>
   </si>
@@ -44,6 +44,9 @@
     <t>平台订单号</t>
   </si>
   <si>
+    <t>波次号</t>
+  </si>
+  <si>
     <t>单据状态</t>
   </si>
   <si>
@@ -114,6 +117,9 @@
   </si>
   <si>
     <t>{.platformCode}</t>
+  </si>
+  <si>
+    <t>{.wavesCode}</t>
   </si>
   <si>
     <t>{.statusName}</t>
@@ -1172,35 +1178,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:X2"/>
+  <dimension ref="A1:Y2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="15" style="2" customWidth="1"/>
     <col min="2" max="2" width="11.375" style="2" customWidth="1"/>
     <col min="3" max="3" width="11.5" style="2" customWidth="1"/>
     <col min="4" max="4" width="12.5" style="2" customWidth="1"/>
-    <col min="5" max="5" width="14.25" style="2" customWidth="1"/>
-    <col min="6" max="6" width="9.75" style="2" customWidth="1"/>
-    <col min="7" max="7" width="11.75" style="2" customWidth="1"/>
-    <col min="8" max="8" width="26.25" style="2" customWidth="1"/>
-    <col min="9" max="10" width="22.75" style="2" customWidth="1"/>
-    <col min="11" max="11" width="10.25" style="2" customWidth="1"/>
-    <col min="12" max="12" width="11.875" style="2" customWidth="1"/>
-    <col min="13" max="13" width="12.125" style="2" customWidth="1"/>
-    <col min="14" max="14" width="11.125" style="2" customWidth="1"/>
-    <col min="15" max="15" width="10.625" style="2" customWidth="1"/>
-    <col min="16" max="16" width="12" style="2" customWidth="1"/>
-    <col min="17" max="17" width="15.375" style="2" customWidth="1"/>
-    <col min="18" max="18" width="10.75" style="2" customWidth="1"/>
-    <col min="19" max="19" width="21.875" style="2" customWidth="1"/>
-    <col min="20" max="20" width="18.25" style="2" customWidth="1"/>
-    <col min="21" max="21" width="17.375" style="2" customWidth="1"/>
-    <col min="22" max="24" width="17.625" style="2" customWidth="1"/>
-    <col min="25" max="27" width="20.625" style="2" customWidth="1"/>
-    <col min="28" max="16384" width="9" style="2"/>
+    <col min="5" max="6" width="14.25" style="2" customWidth="1"/>
+    <col min="7" max="7" width="9.75" style="2" customWidth="1"/>
+    <col min="8" max="8" width="11.75" style="2" customWidth="1"/>
+    <col min="9" max="9" width="26.25" style="2" customWidth="1"/>
+    <col min="10" max="11" width="22.75" style="2" customWidth="1"/>
+    <col min="12" max="12" width="10.25" style="2" customWidth="1"/>
+    <col min="13" max="13" width="11.875" style="2" customWidth="1"/>
+    <col min="14" max="14" width="12.125" style="2" customWidth="1"/>
+    <col min="15" max="15" width="11.125" style="2" customWidth="1"/>
+    <col min="16" max="16" width="10.625" style="2" customWidth="1"/>
+    <col min="17" max="17" width="12" style="2" customWidth="1"/>
+    <col min="18" max="18" width="15.375" style="2" customWidth="1"/>
+    <col min="19" max="19" width="10.75" style="2" customWidth="1"/>
+    <col min="20" max="20" width="21.875" style="2" customWidth="1"/>
+    <col min="21" max="21" width="18.25" style="2" customWidth="1"/>
+    <col min="22" max="22" width="17.375" style="2" customWidth="1"/>
+    <col min="23" max="25" width="17.625" style="2" customWidth="1"/>
+    <col min="26" max="28" width="20.625" style="2" customWidth="1"/>
+    <col min="29" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:24">
+    <row r="1" s="1" customFormat="1" spans="1:25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1273,79 +1279,85 @@
       <c r="X1" s="3" t="s">
         <v>23</v>
       </c>
+      <c r="Y1" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:25">
       <c r="A2" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="S2" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="U2" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="V2" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="W2" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="X2" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="Y2" s="4" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-wms/src/main/resources/excel/b2cDeliveryOrderExport.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/b2cDeliveryOrderExport.xlsx
@@ -119,7 +119,7 @@
     <t>{.platformCode}</t>
   </si>
   <si>
-    <t>{.wavesCode}</t>
+    <t>{.waveCode}</t>
   </si>
   <si>
     <t>{.statusName}</t>
@@ -1186,8 +1186,8 @@
     <col min="3" max="3" width="11.5" style="2" customWidth="1"/>
     <col min="4" max="4" width="12.5" style="2" customWidth="1"/>
     <col min="5" max="6" width="14.25" style="2" customWidth="1"/>
-    <col min="7" max="7" width="9.75" style="2" customWidth="1"/>
-    <col min="8" max="8" width="11.75" style="2" customWidth="1"/>
+    <col min="7" max="7" width="27.375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="20.5" style="2" customWidth="1"/>
     <col min="9" max="9" width="26.25" style="2" customWidth="1"/>
     <col min="10" max="11" width="22.75" style="2" customWidth="1"/>
     <col min="12" max="12" width="10.25" style="2" customWidth="1"/>
